--- a/artfynd/A 50308-2024 artfynd.xlsx
+++ b/artfynd/A 50308-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150067</v>
+        <v>121150066</v>
       </c>
       <c r="B3" t="n">
-        <v>79679</v>
+        <v>92008</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,26 +802,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491629</v>
+        <v>491492</v>
       </c>
       <c r="R3" t="n">
-        <v>6840690</v>
+        <v>6840806</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -900,7 +900,7 @@
         <v>121150063</v>
       </c>
       <c r="B4" t="n">
-        <v>97031</v>
+        <v>97041</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150066</v>
+        <v>121150064</v>
       </c>
       <c r="B5" t="n">
-        <v>91998</v>
+        <v>92008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491492</v>
+        <v>491620</v>
       </c>
       <c r="R5" t="n">
-        <v>6840806</v>
+        <v>6840914</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150064</v>
+        <v>121150067</v>
       </c>
       <c r="B6" t="n">
-        <v>91998</v>
+        <v>79682</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,26 +1135,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491620</v>
+        <v>491629</v>
       </c>
       <c r="R6" t="n">
-        <v>6840914</v>
+        <v>6840690</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 50308-2024 artfynd.xlsx
+++ b/artfynd/A 50308-2024 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150066</v>
+        <v>121150064</v>
       </c>
       <c r="B3" t="n">
         <v>92008</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491492</v>
+        <v>491620</v>
       </c>
       <c r="R3" t="n">
-        <v>6840806</v>
+        <v>6840914</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150063</v>
+        <v>121150066</v>
       </c>
       <c r="B4" t="n">
-        <v>97041</v>
+        <v>92008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,30 +909,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491646</v>
+        <v>491492</v>
       </c>
       <c r="R4" t="n">
-        <v>6841161</v>
+        <v>6840806</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150064</v>
+        <v>121150063</v>
       </c>
       <c r="B5" t="n">
-        <v>92008</v>
+        <v>97041</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,30 +1020,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491620</v>
+        <v>491646</v>
       </c>
       <c r="R5" t="n">
-        <v>6840914</v>
+        <v>6841161</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 50308-2024 artfynd.xlsx
+++ b/artfynd/A 50308-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150064</v>
+        <v>121150067</v>
       </c>
       <c r="B3" t="n">
-        <v>92008</v>
+        <v>79685</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,26 +802,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491620</v>
+        <v>491629</v>
       </c>
       <c r="R3" t="n">
-        <v>6840914</v>
+        <v>6840690</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150066</v>
+        <v>121150063</v>
       </c>
       <c r="B4" t="n">
-        <v>92008</v>
+        <v>97054</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,30 +909,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491492</v>
+        <v>491646</v>
       </c>
       <c r="R4" t="n">
-        <v>6840806</v>
+        <v>6841161</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150063</v>
+        <v>121150064</v>
       </c>
       <c r="B5" t="n">
-        <v>97041</v>
+        <v>92020</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,30 +1020,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491646</v>
+        <v>491620</v>
       </c>
       <c r="R5" t="n">
-        <v>6841161</v>
+        <v>6840914</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150067</v>
+        <v>121150066</v>
       </c>
       <c r="B6" t="n">
-        <v>79682</v>
+        <v>92020</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,26 +1135,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491629</v>
+        <v>491492</v>
       </c>
       <c r="R6" t="n">
-        <v>6840690</v>
+        <v>6840806</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 50308-2024 artfynd.xlsx
+++ b/artfynd/A 50308-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150067</v>
+        <v>121150063</v>
       </c>
       <c r="B3" t="n">
-        <v>79685</v>
+        <v>97055</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491629</v>
+        <v>491646</v>
       </c>
       <c r="R3" t="n">
-        <v>6840690</v>
+        <v>6841161</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150063</v>
+        <v>121150064</v>
       </c>
       <c r="B4" t="n">
-        <v>97054</v>
+        <v>92021</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,30 +909,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491646</v>
+        <v>491620</v>
       </c>
       <c r="R4" t="n">
-        <v>6841161</v>
+        <v>6840914</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150064</v>
+        <v>121150067</v>
       </c>
       <c r="B5" t="n">
-        <v>92020</v>
+        <v>79685</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,26 +1024,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491620</v>
+        <v>491629</v>
       </c>
       <c r="R5" t="n">
-        <v>6840914</v>
+        <v>6840690</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1122,7 +1122,7 @@
         <v>121150066</v>
       </c>
       <c r="B6" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 50308-2024 artfynd.xlsx
+++ b/artfynd/A 50308-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150063</v>
+        <v>121150066</v>
       </c>
       <c r="B3" t="n">
-        <v>97055</v>
+        <v>92024</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,30 +798,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491646</v>
+        <v>491492</v>
       </c>
       <c r="R3" t="n">
-        <v>6841161</v>
+        <v>6840806</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150064</v>
+        <v>121150063</v>
       </c>
       <c r="B4" t="n">
-        <v>92021</v>
+        <v>97058</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,30 +909,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491620</v>
+        <v>491646</v>
       </c>
       <c r="R4" t="n">
-        <v>6840914</v>
+        <v>6841161</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150067</v>
+        <v>121150064</v>
       </c>
       <c r="B5" t="n">
-        <v>79685</v>
+        <v>92024</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,26 +1024,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491629</v>
+        <v>491620</v>
       </c>
       <c r="R5" t="n">
-        <v>6840690</v>
+        <v>6840914</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150066</v>
+        <v>121150067</v>
       </c>
       <c r="B6" t="n">
-        <v>92021</v>
+        <v>79688</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,26 +1135,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491492</v>
+        <v>491629</v>
       </c>
       <c r="R6" t="n">
-        <v>6840806</v>
+        <v>6840690</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 50308-2024 artfynd.xlsx
+++ b/artfynd/A 50308-2024 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150066</v>
+        <v>121150064</v>
       </c>
       <c r="B3" t="n">
         <v>92024</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491492</v>
+        <v>491620</v>
       </c>
       <c r="R3" t="n">
-        <v>6840806</v>
+        <v>6840914</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150063</v>
+        <v>121150066</v>
       </c>
       <c r="B4" t="n">
-        <v>97058</v>
+        <v>92024</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,30 +909,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491646</v>
+        <v>491492</v>
       </c>
       <c r="R4" t="n">
-        <v>6841161</v>
+        <v>6840806</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150064</v>
+        <v>121150067</v>
       </c>
       <c r="B5" t="n">
-        <v>92024</v>
+        <v>79688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,26 +1024,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491620</v>
+        <v>491629</v>
       </c>
       <c r="R5" t="n">
-        <v>6840914</v>
+        <v>6840690</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150067</v>
+        <v>121150063</v>
       </c>
       <c r="B6" t="n">
-        <v>79688</v>
+        <v>97058</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491629</v>
+        <v>491646</v>
       </c>
       <c r="R6" t="n">
-        <v>6840690</v>
+        <v>6841161</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 50308-2024 artfynd.xlsx
+++ b/artfynd/A 50308-2024 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112182863</v>
+        <v>121150064</v>
       </c>
       <c r="B2" t="n">
-        <v>96692</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491561</v>
+        <v>491620</v>
       </c>
       <c r="R2" t="n">
-        <v>6840933</v>
+        <v>6840914</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150064</v>
+        <v>121150066</v>
       </c>
       <c r="B3" t="n">
-        <v>92024</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,7 +811,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491620</v>
+        <v>491492</v>
       </c>
       <c r="R3" t="n">
-        <v>6840914</v>
+        <v>6840806</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150066</v>
+        <v>121150067</v>
       </c>
       <c r="B4" t="n">
-        <v>92024</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,26 +898,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491492</v>
+        <v>491629</v>
       </c>
       <c r="R4" t="n">
-        <v>6840806</v>
+        <v>6840690</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,37 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150067</v>
+        <v>112182863</v>
       </c>
       <c r="B5" t="n">
-        <v>79688</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491629</v>
+        <v>491561</v>
       </c>
       <c r="R5" t="n">
-        <v>6840690</v>
+        <v>6840933</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1122,12 +1102,7 @@
         <v>121150063</v>
       </c>
       <c r="B6" t="n">
-        <v>97058</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
